--- a/backtest_runs/20260410_193731/by_symbol/SML/SML.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SML/SML.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -587,7 +587,7 @@
         <v>-1177.400000000002</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>98822.59999999999</v>
@@ -771,7 +771,7 @@
         <v>-9118.759999999991</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>89703.84000000001</v>
@@ -863,7 +863,7 @@
         <v>-4945.080000000003</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>91222.28</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>91222.28</v>
@@ -1139,7 +1139,7 @@
         <v>-4612.159999999983</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>90166.68000000001</v>
@@ -1231,7 +1231,7 @@
         <v>-6219.920000000009</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>83946.76000000001</v>
@@ -1507,7 +1507,7 @@
         <v>-1559.03999999999</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>97458.44</v>
